--- a/temporario/Apontamento_Luis.xlsx
+++ b/temporario/Apontamento_Luis.xlsx
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="M2" s="75" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="N2" s="37" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="Q2" s="76" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="R2" s="26" t="n"/>
@@ -1480,23 +1480,23 @@
     <row r="4">
       <c r="A4" s="80" t="inlineStr">
         <is>
-          <t>FAT28210767</t>
+          <t>FAT27192434</t>
         </is>
       </c>
       <c r="B4" s="81" t="inlineStr">
         <is>
-          <t>26/02408</t>
+          <t>26/02293</t>
         </is>
       </c>
       <c r="C4" s="82" t="inlineStr">
         <is>
-          <t>IZZAPLAST</t>
+          <t>YUSEN LOGISTICS 2</t>
         </is>
       </c>
       <c r="D4" s="83" t="n"/>
       <c r="E4" s="82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3,5 + 0,5</t>
         </is>
       </c>
       <c r="F4" s="83" t="n"/>
@@ -1515,23 +1515,25 @@
       <c r="S4" s="18" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="86" t="n">
-        <v>24282</v>
+      <c r="A5" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAT28122480 </t>
+        </is>
       </c>
       <c r="B5" s="87" t="inlineStr">
         <is>
-          <t>26/02297</t>
+          <t>26/02319</t>
         </is>
       </c>
       <c r="C5" s="76" t="inlineStr">
         <is>
-          <t xml:space="preserve">LABORATORIO TAYUYNA </t>
+          <t xml:space="preserve"> ECOLAB BARUERI</t>
         </is>
       </c>
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="76" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>2 + 1,5</t>
         </is>
       </c>
       <c r="F5" s="26" t="n"/>
@@ -1550,27 +1552,11 @@
       <c r="S5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAT28136401 </t>
-        </is>
-      </c>
-      <c r="B6" s="87" t="inlineStr">
-        <is>
-          <t>26/02376</t>
-        </is>
-      </c>
-      <c r="C6" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CERAMICA ALLEANZA</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="45" t="n"/>
       <c r="D6" s="26" t="n"/>
-      <c r="E6" s="76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="E6" s="45" t="n"/>
       <c r="F6" s="26" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>

--- a/temporario/Apontamento_Luis.xlsx
+++ b/temporario/Apontamento_Luis.xlsx
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="M2" s="75" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="N2" s="37" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="Q2" s="76" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R2" s="26" t="n"/>
@@ -1480,23 +1480,23 @@
     <row r="4">
       <c r="A4" s="80" t="inlineStr">
         <is>
-          <t>FAT27192434</t>
+          <t>FAT28210767</t>
         </is>
       </c>
       <c r="B4" s="81" t="inlineStr">
         <is>
-          <t>26/02293</t>
+          <t>26/02408</t>
         </is>
       </c>
       <c r="C4" s="82" t="inlineStr">
         <is>
-          <t>YUSEN LOGISTICS 2</t>
+          <t>IZZAPLAST</t>
         </is>
       </c>
       <c r="D4" s="83" t="n"/>
       <c r="E4" s="82" t="inlineStr">
         <is>
-          <t>3,5 + 0,5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" s="83" t="n"/>
@@ -1515,25 +1515,23 @@
       <c r="S4" s="18" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAT28122480 </t>
-        </is>
+      <c r="A5" s="86" t="n">
+        <v>24282</v>
       </c>
       <c r="B5" s="87" t="inlineStr">
         <is>
-          <t>26/02319</t>
+          <t>26/02297</t>
         </is>
       </c>
       <c r="C5" s="76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ECOLAB BARUERI</t>
+          <t xml:space="preserve">LABORATORIO TAYUYNA </t>
         </is>
       </c>
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="76" t="inlineStr">
         <is>
-          <t>2 + 1,5</t>
+          <t>8,3</t>
         </is>
       </c>
       <c r="F5" s="26" t="n"/>
@@ -1552,11 +1550,27 @@
       <c r="S5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="24" t="n"/>
-      <c r="C6" s="45" t="n"/>
+      <c r="A6" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAT28136401 </t>
+        </is>
+      </c>
+      <c r="B6" s="87" t="inlineStr">
+        <is>
+          <t>26/02376</t>
+        </is>
+      </c>
+      <c r="C6" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CERAMICA ALLEANZA</t>
+        </is>
+      </c>
       <c r="D6" s="26" t="n"/>
-      <c r="E6" s="45" t="n"/>
+      <c r="E6" s="76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="F6" s="26" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
